--- a/data/trans_dic/RUIDO_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>70,97; 94,4</t>
+          <t>71,12; 94,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,23; 95,38</t>
+          <t>68,3; 95,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,21; 92,96</t>
+          <t>76,59; 92,56</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,08; 87,92</t>
+          <t>75,95; 88,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,01; 79,53</t>
+          <t>67,84; 79,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,7; 82,17</t>
+          <t>73,91; 82,44</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,38; 71,9</t>
+          <t>55,58; 71,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,72; 77,35</t>
+          <t>60,74; 77,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,59; 72,35</t>
+          <t>61,24; 72,85</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,9; 83,42</t>
+          <t>72,7; 82,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,78; 78,79</t>
+          <t>69,59; 78,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,31; 79,45</t>
+          <t>72,65; 79,4</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>24143</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28840</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52982</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>20192; 26699</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22575; 31484</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>47061; 56871</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>176881</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>192962</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>369842</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>164579; 191395</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>175188; 205185</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>351033; 391515</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>54236</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>66492</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>120729</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>47266; 61185</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57621; 73845</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>110171; 131072</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>255260</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>288294</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>543554</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>239995; 273672</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>268712; 303539</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>520382; 568736</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/RUIDO_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,12; 94,04</t>
+          <t>70,64; 94,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,3; 95,26</t>
+          <t>69,54; 95,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,59; 92,56</t>
+          <t>76,13; 92,57</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,95; 88,33</t>
+          <t>76,23; 88,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,84; 79,46</t>
+          <t>68,15; 79,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,91; 82,44</t>
+          <t>73,46; 82,63</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,58; 71,95</t>
+          <t>54,93; 71,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,74; 77,84</t>
+          <t>61,11; 77,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,24; 72,85</t>
+          <t>60,81; 73,03</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,7; 82,9</t>
+          <t>72,96; 82,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,59; 78,61</t>
+          <t>69,54; 78,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,65; 79,4</t>
+          <t>72,38; 79,46</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20192; 26699</t>
+          <t>20056; 26916</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22575; 31484</t>
+          <t>22985; 31453</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47061; 56871</t>
+          <t>46777; 56876</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>164579; 191395</t>
+          <t>165190; 191144</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>175188; 205185</t>
+          <t>175995; 206168</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>351033; 391515</t>
+          <t>348883; 392450</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47266; 61185</t>
+          <t>46711; 60717</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57621; 73845</t>
+          <t>57976; 73623</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>110171; 131072</t>
+          <t>109394; 131386</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>239995; 273672</t>
+          <t>240862; 272843</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>268712; 303539</t>
+          <t>268513; 303444</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>520382; 568736</t>
+          <t>518404; 569163</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/RUIDO_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>70,64; 94,8</t>
+          <t>66,3; 95,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,54; 95,16</t>
+          <t>67,35; 92,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,13; 92,57</t>
+          <t>73,78; 92,11</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>76,52%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,23; 88,21</t>
+          <t>68,43; 79,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,15; 79,84</t>
+          <t>73,55; 83,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,46; 82,63</t>
+          <t>72,75; 79,92</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,49%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,93; 71,4</t>
+          <t>60,56; 76,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,11; 77,61</t>
+          <t>54,59; 71,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,81; 73,03</t>
+          <t>60,15; 71,82</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>74,56%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,96; 82,65</t>
+          <t>69,8; 78,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,54; 78,58</t>
+          <t>70,71; 78,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,38; 79,46</t>
+          <t>71,4; 77,49</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24143</t>
+          <t>26270</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52982</t>
+          <t>45788</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20056; 26916</t>
+          <t>20086; 28946</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22985; 31453</t>
+          <t>15864; 21874</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46777; 56876</t>
+          <t>39727; 49603</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>236</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>176881</t>
+          <t>178552</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>192962</t>
+          <t>150813</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369842</t>
+          <t>329365</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>165190; 191144</t>
+          <t>163701; 190497</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>175995; 206168</t>
+          <t>140668; 160005</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>348883; 392450</t>
+          <t>313136; 344015</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>85</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54236</t>
+          <t>61789</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66492</t>
+          <t>53853</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120729</t>
+          <t>115642</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46711; 60717</t>
+          <t>53570; 68040</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57976; 73623</t>
+          <t>46664; 61117</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109394; 131386</t>
+          <t>104626; 124914</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>350</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>255260</t>
+          <t>266611</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>288294</t>
+          <t>224185</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>543554</t>
+          <t>490796</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>240862; 272843</t>
+          <t>249873; 282316</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>268513; 303444</t>
+          <t>212332; 236304</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>518404; 569163</t>
+          <t>469980; 510093</t>
         </is>
       </c>
     </row>
